--- a/samples/ss_cbatu12_dltms_ingest.xlsx
+++ b/samples/ss_cbatu12_dltms_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/samples/ss_cbatu12_dltms_ingest.xlsx
+++ b/samples/ss_cbatu12_dltms_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Cibatu 500/150 kV</t>
+          <t>IBT 1 Cibatu 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GITET Deltamas</t>
+          <t>IBT 2 Cibatu 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DLTMS7</t>
+          <t>IBT 2 CBATU7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>500 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CBATU7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CBATU</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -791,51 +805,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 1,2,3,4 Deltamas 500/150 kV</t>
+          <t>GITET Deltamas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 1 DLTMS7</t>
+          <t>DLTMS7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1,2,3,4</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>DLTMS7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>DLTMS</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>4 IBT (unit 1,2,3,4)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -845,14 +841,10 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>4;7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -866,31 +858,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cibatu (bus 150 kV)</t>
+          <t>IBT 1 Deltamas 500/150 kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>IBT 1 DLTMS7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DLTMS7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DLTMS</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -902,10 +908,14 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4;7</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -919,37 +929,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deltamas (bus 150 kV)</t>
+          <t>IBT 2 Deltamas 500/150 kV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>IBT 2 DLTMS7</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>DLTMS7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>DLTMS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -959,10 +979,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4;7</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -976,31 +1000,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PLTGU Bekasi Power</t>
+          <t>IBT 3 Deltamas 500/150 kV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KIT_BKPWR</t>
+          <t>IBT 3 DLTMS7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DLTMS7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DLTMS</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -1012,10 +1050,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4;7</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1029,31 +1071,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTGU Cikarang Listrindo</t>
+          <t>IBT 4 Deltamas 500/150 kV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT_CLNDO</t>
+          <t>IBT 4 DLTMS7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>DLTMS7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DLTMS</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1070,7 +1126,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4;7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1086,12 +1142,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bekasi Power</t>
+          <t>Cibatu (bus 150 kV)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BKPWR</t>
+          <t>CBATU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1139,12 +1195,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cikarang Listrindo</t>
+          <t>Deltamas (bus 150 kV)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLNDO</t>
+          <t>DLTMS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1165,7 +1221,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1192,21 +1252,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jababeka Usin</t>
+          <t>PLTGU Bekasi Power</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JUSIN</t>
+          <t>KIT_BKPWR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1245,21 +1305,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cilegsi</t>
+          <t>PLTGU Cikarang Listrindo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLGSI</t>
+          <t>KIT_CLNDO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1281,10 +1341,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1298,12 +1362,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hankook</t>
+          <t>Bekasi Power</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HNKOK</t>
+          <t>BKPWR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1312,7 +1376,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1334,14 +1398,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1355,12 +1415,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jababeka</t>
+          <t>Cikarang Listrindo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JBBKA</t>
+          <t>CLNDO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1369,7 +1429,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1408,12 +1468,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cikarang</t>
+          <t>Jababeka Usin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CIKRG</t>
+          <t>JUSIN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1461,12 +1521,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cikarang Lippo</t>
+          <t>Cilegsi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CKLPO</t>
+          <t>CLGSI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1497,14 +1557,10 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1518,12 +1574,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sukamahi</t>
+          <t>Hankook</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SKMHI</t>
+          <t>HNKOK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1544,11 +1600,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
@@ -1558,10 +1610,14 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1575,12 +1631,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rejosari</t>
+          <t>Jababeka</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RJPSI</t>
+          <t>JBBKA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1589,7 +1645,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1628,12 +1684,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Meyko Makmur</t>
+          <t>Cikarang</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MYKMK</t>
+          <t>CIKRG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1642,7 +1698,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1681,12 +1737,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fajar Surya Wisesa</t>
+          <t>Cikarang Lippo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FJSWA</t>
+          <t>CKLPO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1695,7 +1751,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1722,7 +1778,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1738,12 +1794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gandamekar</t>
+          <t>Sukamahi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GDMKR</t>
+          <t>SKMHI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1752,7 +1808,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1778,14 +1834,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1799,12 +1851,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>THK</t>
+          <t>Rejosari</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>THK</t>
+          <t>RJPSI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1852,12 +1904,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mega Kaya</t>
+          <t>Meyko Makmur</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MGKYA</t>
+          <t>MYKMK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1905,12 +1957,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pinayungan</t>
+          <t>Fajar Surya Wisesa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PNYGN</t>
+          <t>FJSWA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1919,7 +1971,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1931,11 +1983,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>GI Simpul 4 subsistem; split busbar + kopel</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -1950,7 +1998,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -1966,12 +2014,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tegal Herang</t>
+          <t>Gandamekar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TGHRG</t>
+          <t>GDMKR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1980,7 +2028,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1992,7 +2040,11 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
@@ -2002,10 +2054,14 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2019,12 +2075,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maka Sri (SS Cibatu 3,4)</t>
+          <t>THK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MKSRI</t>
+          <t>THK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2033,7 +2089,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2045,22 +2101,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2080,12 +2128,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suzuki (SS Cibatu 3,4)</t>
+          <t>Mega Kaya</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SZUKI</t>
+          <t>MGKYA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2094,7 +2142,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2106,22 +2154,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2141,12 +2181,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Peruri (SS Cibatu 3,4)</t>
+          <t>Pinayungan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PRURI</t>
+          <t>PNYGN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2155,7 +2195,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2169,7 +2209,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
+          <t>GI Simpul 4 subsistem; split busbar + kopel</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -2178,17 +2218,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2202,12 +2242,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Purwamaya (SS Cibatu 3,4)</t>
+          <t>Tegal Herang</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PRMYA</t>
+          <t>TGHRG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2228,22 +2268,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 3,4</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2263,12 +2295,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tambun (SS New Tambun)</t>
+          <t>Maka Sri (SS Cibatu 3,4)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>MKSRI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2277,7 +2309,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2291,7 +2323,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>batas ke Subsistem New Tambun</t>
+          <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -2317,6 +2349,250 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Suzuki (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SZUKI</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Peruri (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PRURI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Purwamaya (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PRMYA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Tambun (SS New Tambun)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TMBUN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem New Tambun</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3889,12 +4165,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Cibatu-Hankook 1,2 sudah di atas 50% (@57%) jika pasokan PLTG Cikarang Listrindo rendah atau PLN memasok CL</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Cibatu-Hankook 1,2 sudah di atas 50% (@57%) jika pasokan PLTG Cikarang Listrindo rendah atau PLN memasok CL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3924,12 +4200,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Cikarang - Fajar Surya Wisesa sudah di atas 50% (@57%)</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Cikarang - Fajar Surya Wisesa sudah di atas 50% (@57%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3994,12 +4270,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Deltamas-Cikarang Lippo 1,2 sudah di atas 50% (@57%) ketika PLTGU CL dan BP tidak beroperasi</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Deltamas-Cikarang Lippo 1,2 sudah di atas 50% (@57%) ketika PLTGU CL dan BP tidak beroperasi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4029,12 +4305,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Cikarang Lippo- Gandamekar 1,2 sudah di atas 50% (@57%) ketika PLTGU CL dan BP tidak beroperas</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan SUTT 150 kV Cikarang Lippo- Gandamekar 1,2 sudah di atas 50% (@57%) ketika PLTGU CL dan BP tidak beroperas</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4064,12 +4340,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan IBT 1 &amp; 2 GITET Deltamas berpotensi naik diatas 50%</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan IBT 1 &amp; 2 GITET Deltamas berpotensi naik diatas 50%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4099,12 +4375,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Kurang andalnya operasi Split Busbar Busbar GI 150 kV Pinayungan karena GI tersebut menjadi GI Simpul (pertemuan 4 Subsistem yaitu Cibatu 1,2, Cibatu 3,4, Mandirancan 1,2 dan Deltamas 3,4) karena belum tersedianya Bus Section dan Kopel kedua di GI 150 kV Pinayungan</t>
+          <t>[BELUM_DITETAPKAN] Kurang andalnya operasi Split Busbar Busbar GI 150 kV Pinayungan karena GI tersebut menjadi GI Simpul (pertemuan 4 Subsistem yaitu Cibatu 1,2, Cibatu 3,4, Mandirancan 1,2 dan Deltamas 3,4) karena belum tersedianya Bus Section dan Kopel kedua di GI 150 kV Pinayungan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/samples/ss_cbatu12_dltms_ingest.xlsx
+++ b/samples/ss_cbatu12_dltms_ingest.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4079,6 +4080,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feeder (GI Induk)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status Operasi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PRMYA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Purwamaya (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PNYGN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PRURI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Peruri (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PNYGN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SZUKI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Suzuki (SS Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CBATU</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TMBUN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tambun (SS New Tambun)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GDMKR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
